--- a/source/SUEZ/SUEZ_DECH_S2S5_JAN2026.xlsx
+++ b/source/SUEZ/SUEZ_DECH_S2S5_JAN2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amine.saadeddine\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\aminesaadeddine\verif_tonnage_valene\source\SUEZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{116A30AB-0C40-4591-8FC5-579B533EAD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDBBBFA-9A48-494E-91CE-8ED3CF48DD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="301">
-  <si>
-    <t>Date vidage 01/01/2026 - 24/01/2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="378">
+  <si>
+    <t>Date vidage 01/01/2026 - 25/01/2026</t>
   </si>
   <si>
     <t/>
@@ -139,12 +139,18 @@
     <t>01261757</t>
   </si>
   <si>
+    <t>TM7283</t>
+  </si>
+  <si>
     <t>01261804</t>
   </si>
   <si>
     <t>Transport Ferrailles</t>
   </si>
   <si>
+    <t>TM7284</t>
+  </si>
+  <si>
     <t>01261803</t>
   </si>
   <si>
@@ -166,15 +172,24 @@
     <t>DECHETTERIE MLV VAUCOULEURS</t>
   </si>
   <si>
+    <t>TM7285</t>
+  </si>
+  <si>
     <t>01261791</t>
   </si>
   <si>
     <t>ROSA DA SILVA</t>
   </si>
   <si>
+    <t>TM7286</t>
+  </si>
+  <si>
     <t>01261789</t>
   </si>
   <si>
+    <t>TM7288</t>
+  </si>
+  <si>
     <t>01261790</t>
   </si>
   <si>
@@ -184,6 +199,9 @@
     <t>Benne Toit Coulissant 15 mcube</t>
   </si>
   <si>
+    <t>TM7293</t>
+  </si>
+  <si>
     <t>01261805</t>
   </si>
   <si>
@@ -199,6 +217,9 @@
     <t>DECHETTERIE MLJ CLOSEAUX 1</t>
   </si>
   <si>
+    <t>TM7296</t>
+  </si>
+  <si>
     <t>01261810</t>
   </si>
   <si>
@@ -214,6 +235,9 @@
     <t>DECHETTERIE ACHERES</t>
   </si>
   <si>
+    <t>TM7297</t>
+  </si>
+  <si>
     <t>01261807</t>
   </si>
   <si>
@@ -226,12 +250,21 @@
     <t>DECHETTERIE EPONE</t>
   </si>
   <si>
+    <t>TM7298</t>
+  </si>
+  <si>
     <t>01261813</t>
   </si>
   <si>
+    <t>TM7300</t>
+  </si>
+  <si>
     <t>01262122</t>
   </si>
   <si>
+    <t>TM7299</t>
+  </si>
+  <si>
     <t>01262121</t>
   </si>
   <si>
@@ -241,6 +274,9 @@
     <t>DECHETTERIE CONFLANS</t>
   </si>
   <si>
+    <t>TM7295</t>
+  </si>
+  <si>
     <t>BM7401260001</t>
   </si>
   <si>
@@ -346,6 +382,9 @@
     <t>01264268</t>
   </si>
   <si>
+    <t>PRC591414</t>
+  </si>
+  <si>
     <t>01261822</t>
   </si>
   <si>
@@ -355,6 +394,9 @@
     <t>jeudi</t>
   </si>
   <si>
+    <t>TM7325</t>
+  </si>
+  <si>
     <t>01262710</t>
   </si>
   <si>
@@ -367,9 +409,15 @@
     <t>01262732</t>
   </si>
   <si>
+    <t>TM7326</t>
+  </si>
+  <si>
     <t>01264266</t>
   </si>
   <si>
+    <t>TM7323</t>
+  </si>
+  <si>
     <t>01262383</t>
   </si>
   <si>
@@ -391,27 +439,45 @@
     <t>GT-224-NF</t>
   </si>
   <si>
+    <t>TM7330</t>
+  </si>
+  <si>
     <t>01262758</t>
   </si>
   <si>
+    <t>TM7332</t>
+  </si>
+  <si>
     <t>01262891</t>
   </si>
   <si>
     <t>EL GUEHOUDI</t>
   </si>
   <si>
+    <t>TM7340</t>
+  </si>
+  <si>
     <t>01262901</t>
   </si>
   <si>
     <t>TRAORE</t>
   </si>
   <si>
+    <t>TM7338</t>
+  </si>
+  <si>
     <t>BM7401260005</t>
   </si>
   <si>
+    <t>TM7341</t>
+  </si>
+  <si>
     <t>01262925</t>
   </si>
   <si>
+    <t>TM7346</t>
+  </si>
+  <si>
     <t>01262930</t>
   </si>
   <si>
@@ -496,9 +562,6 @@
     <t>12254541</t>
   </si>
   <si>
-    <t>TM7375</t>
-  </si>
-  <si>
     <t>01263764</t>
   </si>
   <si>
@@ -754,6 +817,12 @@
     <t>01264435</t>
   </si>
   <si>
+    <t>PRC592386</t>
+  </si>
+  <si>
+    <t>01265155</t>
+  </si>
+  <si>
     <t>PRC592394</t>
   </si>
   <si>
@@ -802,6 +871,12 @@
     <t>01264573</t>
   </si>
   <si>
+    <t>PRC592550</t>
+  </si>
+  <si>
+    <t>01264578</t>
+  </si>
+  <si>
     <t>PRC592583</t>
   </si>
   <si>
@@ -814,12 +889,30 @@
     <t>01264583</t>
   </si>
   <si>
+    <t>PRC592512</t>
+  </si>
+  <si>
+    <t>01264589</t>
+  </si>
+  <si>
     <t>PRC592485</t>
   </si>
   <si>
     <t>01264579</t>
   </si>
   <si>
+    <t>PRC592529</t>
+  </si>
+  <si>
+    <t>01264590</t>
+  </si>
+  <si>
+    <t>TM7436</t>
+  </si>
+  <si>
+    <t>01264577</t>
+  </si>
+  <si>
     <t>PRC592497</t>
   </si>
   <si>
@@ -838,6 +931,12 @@
     <t>01264575</t>
   </si>
   <si>
+    <t>PRC592503</t>
+  </si>
+  <si>
+    <t>01265159</t>
+  </si>
+  <si>
     <t>PRC592740</t>
   </si>
   <si>
@@ -874,62 +973,194 @@
     <t>01264679</t>
   </si>
   <si>
-    <t>PRC591255</t>
-  </si>
-  <si>
-    <t>PRC591293</t>
-  </si>
-  <si>
-    <t>PRC591294</t>
-  </si>
-  <si>
-    <t>PRC591301</t>
-  </si>
-  <si>
-    <t>PRC591296</t>
-  </si>
-  <si>
-    <t>PRC591299</t>
-  </si>
-  <si>
-    <t>PRC591303</t>
-  </si>
-  <si>
-    <t>PRC591583</t>
-  </si>
-  <si>
-    <t>PRC591555</t>
-  </si>
-  <si>
-    <t>PRC591582</t>
-  </si>
-  <si>
-    <t>PRC591637</t>
-  </si>
-  <si>
-    <t>PRC591662</t>
-  </si>
-  <si>
-    <t>PRC591668</t>
-  </si>
-  <si>
-    <t>PRC591667</t>
-  </si>
-  <si>
-    <t>PRC591669</t>
-  </si>
-  <si>
-    <t>PRC591674</t>
-  </si>
-  <si>
-    <t>PRC591673</t>
+    <t>TM7449</t>
+  </si>
+  <si>
+    <t>01264888</t>
+  </si>
+  <si>
+    <t>PRC592768</t>
+  </si>
+  <si>
+    <t>01264803</t>
+  </si>
+  <si>
+    <t>PRC592808</t>
+  </si>
+  <si>
+    <t>01264799</t>
+  </si>
+  <si>
+    <t>PRC592806</t>
+  </si>
+  <si>
+    <t>01264677</t>
+  </si>
+  <si>
+    <t>PRC592812</t>
+  </si>
+  <si>
+    <t>01264817</t>
+  </si>
+  <si>
+    <t>PRC592802</t>
+  </si>
+  <si>
+    <t>01264793</t>
+  </si>
+  <si>
+    <t>PRC592814</t>
+  </si>
+  <si>
+    <t>01264806</t>
+  </si>
+  <si>
+    <t>TM7452</t>
+  </si>
+  <si>
+    <t>01264922</t>
+  </si>
+  <si>
+    <t>TM7468</t>
+  </si>
+  <si>
+    <t>01265012</t>
+  </si>
+  <si>
+    <t>TM7450</t>
+  </si>
+  <si>
+    <t>01264928</t>
+  </si>
+  <si>
+    <t>TM7453</t>
+  </si>
+  <si>
+    <t>01264921</t>
+  </si>
+  <si>
+    <t>TM7456</t>
+  </si>
+  <si>
+    <t>01265009</t>
+  </si>
+  <si>
+    <t>TM7461</t>
+  </si>
+  <si>
+    <t>01264925</t>
+  </si>
+  <si>
+    <t>TM7462</t>
+  </si>
+  <si>
+    <t>01265008</t>
+  </si>
+  <si>
+    <t>TM7460</t>
+  </si>
+  <si>
+    <t>01264923</t>
+  </si>
+  <si>
+    <t>TM7454</t>
+  </si>
+  <si>
+    <t>01264936</t>
+  </si>
+  <si>
+    <t>TM7455</t>
+  </si>
+  <si>
+    <t>BM0101260006</t>
+  </si>
+  <si>
+    <t>TM7469</t>
+  </si>
+  <si>
+    <t>01265013</t>
+  </si>
+  <si>
+    <t>TM7458</t>
+  </si>
+  <si>
+    <t>01264933</t>
+  </si>
+  <si>
+    <t>TM7466</t>
+  </si>
+  <si>
+    <t>01265010</t>
+  </si>
+  <si>
+    <t>TM7476</t>
+  </si>
+  <si>
+    <t>01265026</t>
+  </si>
+  <si>
+    <t>TM7474</t>
+  </si>
+  <si>
+    <t>01265024</t>
+  </si>
+  <si>
+    <t>TM7477</t>
+  </si>
+  <si>
+    <t>01265016</t>
+  </si>
+  <si>
+    <t>TM7473</t>
+  </si>
+  <si>
+    <t>01265025</t>
+  </si>
+  <si>
+    <t>TM7471</t>
+  </si>
+  <si>
+    <t>01265014</t>
+  </si>
+  <si>
+    <t>TM7470</t>
+  </si>
+  <si>
+    <t>01265020</t>
+  </si>
+  <si>
+    <t>TM7475</t>
+  </si>
+  <si>
+    <t>01265015</t>
+  </si>
+  <si>
+    <t>TM7472</t>
+  </si>
+  <si>
+    <t>01265023</t>
+  </si>
+  <si>
+    <t>TM7478</t>
+  </si>
+  <si>
+    <t>01265153</t>
+  </si>
+  <si>
+    <t>TM7479</t>
+  </si>
+  <si>
+    <t>01265017</t>
+  </si>
+  <si>
+    <t>PRC591977</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -961,21 +1192,8 @@
       <sz val="8"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -983,23 +1201,12 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor rgb="FF92FFD3"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92FFD3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="50"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1035,24 +1242,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1072,27 +1266,14 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1428,7 +1609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.85546875" bestFit="1" customWidth="1"/>
@@ -1515,8 +1696,8 @@
       <c r="G4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>284</v>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>21</v>
@@ -1553,8 +1734,8 @@
       <c r="G5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>29</v>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>28</v>
@@ -1591,8 +1772,8 @@
       <c r="G6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>33</v>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>30</v>
@@ -1629,8 +1810,8 @@
       <c r="G7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>27</v>
+      <c r="H7" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>34</v>
@@ -1667,7 +1848,7 @@
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -1705,11 +1886,11 @@
       <c r="G9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>285</v>
+      <c r="H9" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>22</v>
@@ -1732,7 +1913,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>17</v>
@@ -1743,11 +1924,11 @@
       <c r="G10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>286</v>
+      <c r="H10" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>22</v>
@@ -1767,7 +1948,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>16</v>
@@ -1781,17 +1962,17 @@
       <c r="G11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>287</v>
+      <c r="H11" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L11" s="6">
         <v>0.56000000000000005</v>
@@ -1805,7 +1986,7 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>16</v>
@@ -1817,16 +1998,16 @@
         <v>18</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>23</v>
@@ -1843,7 +2024,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>24</v>
@@ -1855,16 +2036,16 @@
         <v>25</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>288</v>
+        <v>49</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>23</v>
@@ -1881,10 +2062,10 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -1893,16 +2074,16 @@
         <v>25</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>289</v>
+        <v>49</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>23</v>
@@ -1919,31 +2100,31 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="10" t="s">
-        <v>290</v>
+      <c r="H15" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L15" s="6">
         <v>3.26</v>
@@ -1957,10 +2138,10 @@
         <v>14</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>17</v>
@@ -1969,17 +2150,19 @@
         <v>18</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="12"/>
+        <v>64</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>65</v>
+      </c>
       <c r="I16" s="7" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L16" s="9">
         <v>1.04</v>
@@ -1993,10 +2176,10 @@
         <v>14</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>17</v>
@@ -2005,17 +2188,19 @@
         <v>25</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="13"/>
+        <v>70</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="I17" s="7" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L17" s="9">
         <v>4.5599999999999996</v>
@@ -2029,10 +2214,10 @@
         <v>14</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>17</v>
@@ -2041,11 +2226,13 @@
         <v>25</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" s="13"/>
+        <v>75</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>76</v>
+      </c>
       <c r="I18" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>22</v>
@@ -2065,10 +2252,10 @@
         <v>14</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>17</v>
@@ -2079,9 +2266,11 @@
       <c r="G19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="13"/>
+      <c r="H19" s="7" t="s">
+        <v>78</v>
+      </c>
       <c r="I19" s="7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>22</v>
@@ -2101,10 +2290,10 @@
         <v>14</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>17</v>
@@ -2115,9 +2304,11 @@
       <c r="G20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="13"/>
+      <c r="H20" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="I20" s="7" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>22</v>
@@ -2137,29 +2328,31 @@
         <v>14</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="13"/>
+        <v>83</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>84</v>
+      </c>
       <c r="I21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>65</v>
-      </c>
       <c r="K21" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L21" s="9">
         <v>5.44</v>
@@ -2173,7 +2366,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>16</v>
@@ -2185,19 +2378,19 @@
         <v>18</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L22" s="6">
         <v>1.42</v>
@@ -2211,7 +2404,7 @@
         <v>14</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>24</v>
@@ -2223,19 +2416,19 @@
         <v>25</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L23" s="6">
         <v>5.24</v>
@@ -2249,7 +2442,7 @@
         <v>14</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>24</v>
@@ -2261,19 +2454,19 @@
         <v>25</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>80</v>
+        <v>91</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L24" s="6">
         <v>4.6399999999999997</v>
@@ -2287,7 +2480,7 @@
         <v>14</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>24</v>
@@ -2299,19 +2492,19 @@
         <v>25</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>83</v>
+        <v>64</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L25" s="6">
         <v>3.68</v>
@@ -2325,7 +2518,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>24</v>
@@ -2337,19 +2530,19 @@
         <v>25</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>87</v>
+        <v>49</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L26" s="6">
         <v>2.92</v>
@@ -2363,7 +2556,7 @@
         <v>14</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>35</v>
@@ -2375,19 +2568,19 @@
         <v>25</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>90</v>
+        <v>101</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L27" s="6">
         <v>2.92</v>
@@ -2401,7 +2594,7 @@
         <v>14</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>35</v>
@@ -2413,19 +2606,19 @@
         <v>25</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>92</v>
+        <v>101</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L28" s="6">
         <v>3.92</v>
@@ -2439,7 +2632,7 @@
         <v>14</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>35</v>
@@ -2451,19 +2644,19 @@
         <v>25</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>94</v>
+        <v>49</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L29" s="6">
         <v>3.02</v>
@@ -2477,31 +2670,31 @@
         <v>14</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="L30" s="6">
         <v>1.92</v>
@@ -2515,7 +2708,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>16</v>
@@ -2527,19 +2720,19 @@
         <v>25</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="11" t="s">
-        <v>99</v>
+        <v>83</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L31" s="6">
         <v>1.58</v>
@@ -2553,7 +2746,7 @@
         <v>14</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>24</v>
@@ -2562,22 +2755,22 @@
         <v>17</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>102</v>
+      <c r="H32" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L32" s="6">
         <v>4.74</v>
@@ -2591,7 +2784,7 @@
         <v>14</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>35</v>
@@ -2605,17 +2798,17 @@
       <c r="G33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H33" s="11" t="s">
-        <v>106</v>
+      <c r="H33" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L33" s="6">
         <v>3.8</v>
@@ -2629,10 +2822,10 @@
         <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>17</v>
@@ -2641,19 +2834,19 @@
         <v>25</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>291</v>
+        <v>91</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L34" s="6">
         <v>2.56</v>
@@ -2667,7 +2860,7 @@
         <v>14</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>16</v>
@@ -2679,19 +2872,19 @@
         <v>25</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>113</v>
+        <v>91</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="L35" s="6">
         <v>0.82</v>
@@ -2705,7 +2898,7 @@
         <v>14</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>24</v>
@@ -2717,19 +2910,19 @@
         <v>25</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>292</v>
+        <v>64</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L36" s="6">
         <v>3.46</v>
@@ -2743,31 +2936,31 @@
         <v>14</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H37" s="10" t="s">
-        <v>293</v>
+      <c r="H37" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="L37" s="6">
         <v>2.62</v>
@@ -2781,31 +2974,31 @@
         <v>14</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>117</v>
+        <v>101</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L38" s="6">
         <v>2.68</v>
@@ -2831,19 +3024,19 @@
         <v>18</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H39" s="11" t="s">
-        <v>119</v>
+        <v>49</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L39" s="6">
         <v>0.54</v>
@@ -2866,22 +3059,22 @@
         <v>17</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>294</v>
+      <c r="H40" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L40" s="6">
         <v>1.58</v>
@@ -2904,22 +3097,22 @@
         <v>17</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="11" t="s">
-        <v>1</v>
+      <c r="H41" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L41" s="6">
         <v>5.34</v>
@@ -2933,7 +3126,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>16</v>
@@ -2947,17 +3140,17 @@
       <c r="G42" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H42" s="10" t="s">
-        <v>295</v>
+      <c r="H42" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L42" s="6">
         <v>1</v>
@@ -2971,7 +3164,7 @@
         <v>14</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>24</v>
@@ -2985,17 +3178,17 @@
       <c r="G43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>296</v>
+      <c r="H43" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L43" s="6">
         <v>4.26</v>
@@ -3009,7 +3202,7 @@
         <v>14</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>24</v>
@@ -3018,22 +3211,22 @@
         <v>17</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>297</v>
+        <v>83</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L44" s="6">
         <v>3.48</v>
@@ -3047,7 +3240,7 @@
         <v>14</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>35</v>
@@ -3061,17 +3254,17 @@
       <c r="G45" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H45" s="11" t="s">
-        <v>298</v>
+      <c r="H45" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L45" s="6">
         <v>3.98</v>
@@ -3085,10 +3278,10 @@
         <v>14</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>17</v>
@@ -3097,19 +3290,19 @@
         <v>25</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H46" s="14" t="s">
-        <v>299</v>
+        <v>70</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>151</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L46" s="9">
         <v>6.28</v>
@@ -3123,31 +3316,31 @@
         <v>14</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="H47" s="13" t="s">
-        <v>300</v>
+        <v>153</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L47" s="9">
         <v>4.46</v>
@@ -3161,7 +3354,7 @@
         <v>14</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>16</v>
@@ -3173,19 +3366,19 @@
         <v>18</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L48" s="6">
         <v>0.96</v>
@@ -3199,7 +3392,7 @@
         <v>14</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>24</v>
@@ -3214,16 +3407,16 @@
         <v>26</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L49" s="6">
         <v>6.64</v>
@@ -3237,7 +3430,7 @@
         <v>14</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>24</v>
@@ -3252,16 +3445,16 @@
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L50" s="6">
         <v>5.58</v>
@@ -3275,7 +3468,7 @@
         <v>14</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>24</v>
@@ -3287,19 +3480,19 @@
         <v>25</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L51" s="6">
         <v>4.3600000000000003</v>
@@ -3313,7 +3506,7 @@
         <v>14</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>24</v>
@@ -3322,22 +3515,22 @@
         <v>17</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="L52" s="6">
         <v>4.28</v>
@@ -3351,7 +3544,7 @@
         <v>14</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>35</v>
@@ -3366,16 +3559,16 @@
         <v>36</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="L53" s="6">
         <v>3.02</v>
@@ -3389,7 +3582,7 @@
         <v>14</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>16</v>
@@ -3404,16 +3597,16 @@
         <v>19</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L54" s="6">
         <v>0.9</v>
@@ -3427,7 +3620,7 @@
         <v>14</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>16</v>
@@ -3436,22 +3629,22 @@
         <v>17</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="L55" s="6">
         <v>0.66</v>
@@ -3465,31 +3658,31 @@
         <v>14</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L56" s="6">
         <v>2.92</v>
@@ -3503,7 +3696,7 @@
         <v>14</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>16</v>
@@ -3515,19 +3708,19 @@
         <v>25</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L57" s="6">
         <v>1.3</v>
@@ -3541,7 +3734,7 @@
         <v>14</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>16</v>
@@ -3556,16 +3749,16 @@
         <v>26</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L58" s="6">
         <v>2.04</v>
@@ -3579,7 +3772,7 @@
         <v>14</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>16</v>
@@ -3591,19 +3784,19 @@
         <v>18</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>158</v>
+        <v>377</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L59" s="6">
         <v>0.7</v>
@@ -3617,7 +3810,7 @@
         <v>14</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>16</v>
@@ -3629,19 +3822,19 @@
         <v>18</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L60" s="6">
         <v>0.7</v>
@@ -3655,7 +3848,7 @@
         <v>14</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>24</v>
@@ -3670,16 +3863,16 @@
         <v>26</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L61" s="6">
         <v>3.88</v>
@@ -3693,7 +3886,7 @@
         <v>14</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>24</v>
@@ -3705,19 +3898,19 @@
         <v>25</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L62" s="6">
         <v>4.9000000000000004</v>
@@ -3731,7 +3924,7 @@
         <v>14</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>24</v>
@@ -3743,19 +3936,19 @@
         <v>25</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L63" s="6">
         <v>3.42</v>
@@ -3769,7 +3962,7 @@
         <v>14</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>24</v>
@@ -3781,19 +3974,19 @@
         <v>25</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L64" s="6">
         <v>4.88</v>
@@ -3807,7 +4000,7 @@
         <v>14</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>24</v>
@@ -3819,19 +4012,19 @@
         <v>25</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L65" s="6">
         <v>2.8</v>
@@ -3845,7 +4038,7 @@
         <v>14</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>35</v>
@@ -3860,16 +4053,16 @@
         <v>26</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L66" s="6">
         <v>5.84</v>
@@ -3883,7 +4076,7 @@
         <v>14</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>35</v>
@@ -3895,19 +4088,19 @@
         <v>25</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L67" s="6">
         <v>5.44</v>
@@ -3921,7 +4114,7 @@
         <v>14</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>24</v>
@@ -3933,19 +4126,19 @@
         <v>25</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="L68" s="6">
         <v>2.9</v>
@@ -3959,7 +4152,7 @@
         <v>14</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>24</v>
@@ -3971,19 +4164,19 @@
         <v>25</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="L69" s="6">
         <v>5.5</v>
@@ -3997,7 +4190,7 @@
         <v>14</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>24</v>
@@ -4012,16 +4205,16 @@
         <v>19</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L70" s="6">
         <v>7</v>
@@ -4035,7 +4228,7 @@
         <v>14</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>24</v>
@@ -4047,19 +4240,19 @@
         <v>25</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L71" s="6">
         <v>5.14</v>
@@ -4073,7 +4266,7 @@
         <v>14</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>24</v>
@@ -4082,22 +4275,22 @@
         <v>17</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L72" s="6">
         <v>5.62</v>
@@ -4111,7 +4304,7 @@
         <v>14</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>35</v>
@@ -4126,16 +4319,16 @@
         <v>19</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L73" s="6">
         <v>4.82</v>
@@ -4149,7 +4342,7 @@
         <v>14</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>35</v>
@@ -4161,19 +4354,19 @@
         <v>25</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L74" s="6">
         <v>3.8</v>
@@ -4187,31 +4380,31 @@
         <v>14</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L75" s="6">
         <v>5.44</v>
@@ -4237,19 +4430,19 @@
         <v>25</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="L76" s="6">
         <v>4.12</v>
@@ -4278,16 +4471,16 @@
         <v>36</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="L77" s="6">
         <v>3.3</v>
@@ -4313,19 +4506,19 @@
         <v>25</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L78" s="6">
         <v>3.78</v>
@@ -4339,7 +4532,7 @@
         <v>14</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>16</v>
@@ -4357,13 +4550,13 @@
         <v>20</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L79" s="6">
         <v>0.68</v>
@@ -4377,7 +4570,7 @@
         <v>14</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>16</v>
@@ -4389,19 +4582,19 @@
         <v>18</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L80" s="6">
         <v>0.57999999999999996</v>
@@ -4415,7 +4608,7 @@
         <v>14</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>16</v>
@@ -4427,19 +4620,19 @@
         <v>18</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L81" s="6">
         <v>0.48</v>
@@ -4453,7 +4646,7 @@
         <v>14</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>24</v>
@@ -4471,13 +4664,13 @@
         <v>20</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L82" s="6">
         <v>4.16</v>
@@ -4491,7 +4684,7 @@
         <v>14</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>24</v>
@@ -4503,19 +4696,19 @@
         <v>25</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>1</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L83" s="6">
         <v>2.36</v>
@@ -4529,7 +4722,7 @@
         <v>14</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>24</v>
@@ -4541,19 +4734,19 @@
         <v>25</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L84" s="6">
         <v>3.28</v>
@@ -4567,7 +4760,7 @@
         <v>14</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>24</v>
@@ -4576,7 +4769,7 @@
         <v>17</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>36</v>
@@ -4585,13 +4778,13 @@
         <v>20</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L85" s="6">
         <v>4.78</v>
@@ -4605,7 +4798,7 @@
         <v>14</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>35</v>
@@ -4617,19 +4810,19 @@
         <v>25</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>20</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L86" s="6">
         <v>5.82</v>
@@ -4643,7 +4836,7 @@
         <v>14</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>35</v>
@@ -4661,13 +4854,13 @@
         <v>20</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L87" s="6">
         <v>3.54</v>
@@ -4681,10 +4874,10 @@
         <v>14</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>17</v>
@@ -4699,13 +4892,13 @@
         <v>20</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="J88" s="7" t="s">
         <v>22</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L88" s="9">
         <v>0.5</v>
@@ -4719,10 +4912,10 @@
         <v>14</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>17</v>
@@ -4731,19 +4924,19 @@
         <v>25</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="J89" s="7" t="s">
         <v>22</v>
       </c>
       <c r="K89" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L89" s="9">
         <v>2.46</v>
@@ -4757,10 +4950,10 @@
         <v>14</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>17</v>
@@ -4775,13 +4968,13 @@
         <v>20</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="J90" s="7" t="s">
         <v>22</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L90" s="9">
         <v>3.74</v>
@@ -4795,10 +4988,10 @@
         <v>14</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>17</v>
@@ -4813,13 +5006,13 @@
         <v>20</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="J91" s="7" t="s">
         <v>22</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L91" s="9">
         <v>3.48</v>
@@ -4833,31 +5026,31 @@
         <v>14</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="J92" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K92" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L92" s="9">
         <v>5.8</v>
@@ -4871,31 +5064,31 @@
         <v>14</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K93" s="7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="L93" s="9">
         <v>4.66</v>
@@ -4909,10 +5102,10 @@
         <v>14</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>17</v>
@@ -4927,13 +5120,13 @@
         <v>20</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="J94" s="7" t="s">
         <v>22</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L94" s="9">
         <v>2.16</v>
@@ -4947,10 +5140,10 @@
         <v>14</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>17</v>
@@ -4965,13 +5158,13 @@
         <v>20</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="J95" s="7" t="s">
         <v>22</v>
       </c>
       <c r="K95" s="7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L95" s="9">
         <v>3.62</v>
@@ -4985,7 +5178,7 @@
         <v>14</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>16</v>
@@ -4994,16 +5187,16 @@
         <v>17</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>31</v>
@@ -5023,7 +5216,7 @@
         <v>14</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>24</v>
@@ -5035,19 +5228,19 @@
         <v>25</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="L97" s="6">
         <v>5.94</v>
@@ -5061,7 +5254,7 @@
         <v>14</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>24</v>
@@ -5079,13 +5272,13 @@
         <v>1</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>22</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L98" s="6">
         <v>0</v>
@@ -5099,7 +5292,7 @@
         <v>14</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>24</v>
@@ -5111,19 +5304,19 @@
         <v>25</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L99" s="6">
         <v>2.42</v>
@@ -5137,7 +5330,7 @@
         <v>14</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>35</v>
@@ -5152,16 +5345,16 @@
         <v>36</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L100" s="6">
         <v>3.4</v>
@@ -5175,7 +5368,7 @@
         <v>14</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>35</v>
@@ -5190,16 +5383,16 @@
         <v>36</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L101" s="6">
         <v>5.0999999999999996</v>
@@ -5213,7 +5406,7 @@
         <v>14</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>35</v>
@@ -5225,19 +5418,19 @@
         <v>25</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L102" s="6">
         <v>4.4400000000000004</v>
@@ -5251,7 +5444,7 @@
         <v>14</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>35</v>
@@ -5263,19 +5456,19 @@
         <v>25</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L103" s="6">
         <v>3.96</v>
@@ -5289,31 +5482,31 @@
         <v>14</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K104" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="L104" s="6">
         <v>3.72</v>
@@ -5327,31 +5520,31 @@
         <v>14</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L105" s="6">
         <v>4.46</v>
@@ -5365,7 +5558,7 @@
         <v>14</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>16</v>
@@ -5383,13 +5576,13 @@
         <v>1</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L106" s="6">
         <v>0</v>
@@ -5403,7 +5596,7 @@
         <v>14</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>16</v>
@@ -5415,19 +5608,19 @@
         <v>18</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L107" s="6">
         <v>0.59</v>
@@ -5441,7 +5634,7 @@
         <v>14</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>24</v>
@@ -5456,16 +5649,16 @@
         <v>26</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="L108" s="6">
         <v>4.0599999999999996</v>
@@ -5479,7 +5672,7 @@
         <v>14</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>24</v>
@@ -5494,16 +5687,16 @@
         <v>19</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L109" s="6">
         <v>4.68</v>
@@ -5517,7 +5710,7 @@
         <v>14</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>24</v>
@@ -5529,22 +5722,22 @@
         <v>25</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L110" s="6">
-        <v>5.62</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5555,34 +5748,34 @@
         <v>14</v>
       </c>
       <c r="C111" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K111" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="L111" s="6">
-        <v>1.9</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5593,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>35</v>
@@ -5605,22 +5798,22 @@
         <v>25</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="L112" s="6">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -5631,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>35</v>
@@ -5643,22 +5836,22 @@
         <v>25</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L113" s="6">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5669,34 +5862,34 @@
         <v>14</v>
       </c>
       <c r="C114" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K114" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="L114" s="6">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5707,34 +5900,34 @@
         <v>14</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="L115" s="6">
-        <v>4.76</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5745,72 +5938,72 @@
         <v>14</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="L116" s="6">
-        <v>3</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="L117" s="6">
-        <v>0.97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5821,7 +6014,7 @@
         <v>14</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>16</v>
@@ -5833,22 +6026,22 @@
         <v>18</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="L118" s="6">
-        <v>0.47</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5859,34 +6052,34 @@
         <v>14</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L119" s="6">
-        <v>6.4</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5897,34 +6090,34 @@
         <v>14</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="L120" s="6">
-        <v>2.12</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5935,10 +6128,10 @@
         <v>14</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>17</v>
@@ -5947,22 +6140,22 @@
         <v>25</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="L121" s="6">
-        <v>4.28</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5973,10 +6166,10 @@
         <v>14</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>17</v>
@@ -5985,22 +6178,22 @@
         <v>25</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="K122" s="2" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="L122" s="6">
-        <v>3.96</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -6011,86 +6204,86 @@
         <v>14</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="L123" s="6">
-        <v>3.02</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="L124" s="6">
-        <v>0.6</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>17</v>
@@ -6099,36 +6292,36 @@
         <v>25</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L125" s="6">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>17</v>
@@ -6137,36 +6330,36 @@
         <v>25</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="L126" s="6">
-        <v>3.62</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>17</v>
@@ -6175,135 +6368,1503 @@
         <v>25</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="L127" s="6">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="K128" s="2" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="L128" s="6">
-        <v>6.4</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
+        <v>46043</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L129" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
         <v>46044</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D129" s="2" t="s">
+      <c r="B130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L130" s="6">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
+        <v>46044</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L131" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
+        <v>46044</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L132" s="6">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
+        <v>46044</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L133" s="6">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
+        <v>46044</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="L134" s="6">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
+        <v>46044</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D135" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E129" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J129" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L129" s="6">
+      <c r="E135" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L135" s="6">
         <v>1.52</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L136" s="6">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L137" s="6">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L138" s="6">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K139" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L139" s="6">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L140" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L141" s="6">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L142" s="6">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L143" s="6">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L144" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L145" s="6">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L146" s="6">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L147" s="6">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L148" s="6">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L149" s="6">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L150" s="6">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L151" s="6">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L152" s="6">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L153" s="6">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L154" s="6">
+        <v>4.5199999999999996</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" s="3">
+        <v>46046</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L155" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="J156" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K156" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L156" s="9">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="J157" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K157" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L157" s="9">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="J158" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K158" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L158" s="9">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="J159" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K159" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L159" s="9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="I160" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="J160" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K160" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L160" s="9">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="I161" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="J161" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K161" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L161" s="9">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="J162" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K162" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L162" s="9">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="J163" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K163" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L163" s="9">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="J164" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K164" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="L164" s="9">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" s="8">
+        <v>46047</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="I165" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="J165" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K165" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L165" s="9">
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D130" s="4" t="s">
+      <c r="D166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E130" s="4" t="s">
+      <c r="E166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F130" s="4" t="s">
+      <c r="F166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H130" s="4" t="s">
+      <c r="H166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I130" s="4" t="s">
+      <c r="I166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="J130" s="4" t="s">
+      <c r="J166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K130" s="4" t="s">
+      <c r="K166" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="L130" s="4" t="s">
+      <c r="L166" s="4" t="s">
         <v>1</v>
       </c>
     </row>
